--- a/Templates/bulkImport/config/construct_LA_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_LA_config_sslr.xlsx
@@ -1,90 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9024"/>
   </bookViews>
   <sheets>
     <sheet name="LA_config_sslr" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="C5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Times New Roman"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Times New Roman"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Date Format:
-2024-01-01
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>*</t>
   </si>
@@ -101,9 +31,6 @@
     <t>c_ref_no</t>
   </si>
   <si>
-    <t>c_site_doc_ref_no</t>
-  </si>
-  <si>
     <t>c_date_issued</t>
   </si>
   <si>
@@ -143,70 +70,13 @@
     <t>c_date_received</t>
   </si>
   <si>
-    <t>c_file</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Reference No. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <t>Site Document Reference No.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Date Issued </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Section </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
+    <t>Reference No.</t>
+  </si>
+  <si>
+    <t>Date Issued</t>
+  </si>
+  <si>
+    <t>Section</t>
   </si>
   <si>
     <t>Total KM Run</t>
@@ -240,22 +110,19 @@
   </si>
   <si>
     <t>Date Received</t>
-  </si>
-  <si>
-    <t>Attachment(Letters &amp; Drawing)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -412,19 +279,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1227,30 +1081,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P5"/>
-  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="2" width="14.8518518518519" customWidth="1"/>
-    <col min="3" max="5" width="14.712962962963" customWidth="1"/>
-    <col min="6" max="6" width="14.8518518518519" customWidth="1"/>
-    <col min="7" max="7" width="14.287037037037" customWidth="1"/>
-    <col min="8" max="8" width="8.85185185185185" customWidth="1"/>
-    <col min="9" max="15" width="16.5740740740741" customWidth="1"/>
-    <col min="16" max="16" width="29.287037037037" customWidth="1"/>
+    <col min="1" max="1" width="14.8888888888889" customWidth="1"/>
+    <col min="2" max="4" width="14.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="14.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="14.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="8.88888888888889" customWidth="1"/>
+    <col min="8" max="8" width="10.8888888888889" customWidth="1"/>
+    <col min="9" max="9" width="14.3333333333333" customWidth="1"/>
+    <col min="10" max="10" width="8.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1264,10 +1119,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
         <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
@@ -1279,28 +1134,22 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" t="s">
         <v>3</v>
       </c>
-      <c r="P2" t="s">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1343,14 +1192,8 @@
       <c r="N3">
         <v>13</v>
       </c>
-      <c r="O3">
-        <v>14</v>
-      </c>
-      <c r="P3">
-        <v>15</v>
-      </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1393,61 +1236,49 @@
       <c r="N4" t="s">
         <v>17</v>
       </c>
-      <c r="O4" t="s">
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="P4" t="s">
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>26</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>27</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>28</v>
       </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
         <v>29</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>30</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>31</v>
-      </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1455,6 +1286,5 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Templates/bulkImport/config/construct_LA_config_sslr.xlsx
+++ b/Templates/bulkImport/config/construct_LA_config_sslr.xlsx
@@ -1,20 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9024"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="LA_config_sslr" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Times New Roman"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">Date Format:
+2024-01-01
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <si>
     <t>*</t>
   </si>
@@ -31,6 +101,9 @@
     <t>c_ref_no</t>
   </si>
   <si>
+    <t>c_site_doc_ref_no</t>
+  </si>
+  <si>
     <t>c_date_issued</t>
   </si>
   <si>
@@ -70,13 +143,70 @@
     <t>c_date_received</t>
   </si>
   <si>
-    <t>Reference No.</t>
-  </si>
-  <si>
-    <t>Date Issued</t>
-  </si>
-  <si>
-    <t>Section</t>
+    <t>c_file</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Reference No. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>Site Document Reference No.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Date Issued </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Section </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
   </si>
   <si>
     <t>Total KM Run</t>
@@ -110,19 +240,22 @@
   </si>
   <si>
     <t>Date Received</t>
+  </si>
+  <si>
+    <t>Attachment(Letters &amp; Drawing)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -279,6 +412,19 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1081,31 +1227,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="10.3333333333333" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr defaultColWidth="10.287037037037" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="14.8888888888889" customWidth="1"/>
-    <col min="2" max="4" width="14.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="14.8888888888889" customWidth="1"/>
-    <col min="6" max="6" width="14.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="8.88888888888889" customWidth="1"/>
-    <col min="8" max="8" width="10.8888888888889" customWidth="1"/>
-    <col min="9" max="9" width="14.3333333333333" customWidth="1"/>
-    <col min="10" max="10" width="8.66666666666667" customWidth="1"/>
+    <col min="1" max="2" width="14.8518518518519" customWidth="1"/>
+    <col min="3" max="5" width="14.712962962963" customWidth="1"/>
+    <col min="6" max="6" width="14.8518518518519" customWidth="1"/>
+    <col min="7" max="7" width="14.287037037037" customWidth="1"/>
+    <col min="8" max="8" width="8.85185185185185" customWidth="1"/>
+    <col min="9" max="15" width="16.5740740740741" customWidth="1"/>
+    <col min="16" max="16" width="29.287037037037" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1119,10 +1264,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
@@ -1134,22 +1279,28 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
         <v>3</v>
       </c>
-      <c r="K2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" t="s">
-        <v>3</v>
+      <c r="P2" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1192,8 +1343,14 @@
       <c r="N3">
         <v>13</v>
       </c>
+      <c r="O3">
+        <v>14</v>
+      </c>
+      <c r="P3">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1236,49 +1393,61 @@
       <c r="N4" t="s">
         <v>17</v>
       </c>
+      <c r="O4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P4" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="O5" t="s">
+        <v>34</v>
+      </c>
+      <c r="P5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1286,5 +1455,6 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>